--- a/datos/plantilla_gastos.xlsx
+++ b/datos/plantilla_gastos.xlsx
@@ -37,7 +37,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001B45D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,13 +72,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -440,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -450,7 +457,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -618,7 +625,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -627,7 +634,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Cena con cliente; incluye dos copas de vino</t>
+          <t>Cena de trabajo</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -649,30 +656,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>transporte</t>
+          <t>dietas</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Tren del aeropuerto al centro</t>
+          <t>Cena de trabajo con Elena Soto directora de compras de Nortek para cerrar la renovación del contrato</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -708,7 +715,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>29.9</v>
+        <v>28</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -717,7 +724,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Comida de trabajo</t>
+          <t>Comida de trabajo en La Tasquita</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -739,7 +746,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -753,7 +760,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -762,7 +769,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Comida de trabajo</t>
+          <t>Comida de trabajo en La Tasquita</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -807,7 +814,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Billete de avion en clase business</t>
+          <t>Billete de avión en clase business</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -869,26 +876,26 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Clara Vega</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>alojamiento</t>
+          <t>dietas</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Bilbao</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -897,7 +904,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Hotel una noche</t>
+          <t>Almuerzo de equipo</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -959,26 +966,26 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Clara Vega</t>
+          <t>Ana Ruiz</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>dietas</t>
+          <t>alojamiento</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Bilbao</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -987,7 +994,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Almuerzo de equipo</t>
+          <t>Hotel una noche</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1036,6 +1043,456 @@
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>G-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Luis Pardo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>otros</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Varios</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>G-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Marta Gil</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>dietas</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Comida con el equipo de compras de Alvasa para presentar la nueva gama</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>E-001</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ana Ruiz</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>E-002</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Ana Ruiz</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>E-003</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Luis Pardo</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante South Summit en La Nave</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>E-004</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Luis Pardo</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante Sports Summit Madrid</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>E-005</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Marta Gil</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>E-006</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Marta Gil</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>E-007</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sanz</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante el Foro BAIDATA, Semana de la Economía del Dato</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>E-008</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sanz</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante la Feria Internacional del Calzado de Bilbao</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1060,16 +1517,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Plantilla de gastos - Agente de control de gastos</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Plantilla de gastos · Agente de control de gastos</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rellena la hoja 'Gastos' y subela en la aplicacion.</t>
+          <t>Rellena la hoja 'Gastos' y súbela en la aplicación.</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1544,7 @@
       <c r="A4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Reglas del fichero</t>
         </is>
@@ -1103,97 +1560,114 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>- Maximo 40 filas de datos.</t>
+          <t>- Máximo 40 filas de datos.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>- fecha: formato AAAA-MM-DD (por ejemplo 2026-09-02).</t>
+          <t>- fecha: formato AAAA-MM-DD.   - categoria: alojamiento, dietas, transporte u otros.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>- categoria: alojamiento, dietas, transporte u otros.</t>
+          <t>- importe: solo el número.   - moneda: EUR, GBP...   - justificante: S o N.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>- importe: solo el numero, sin simbolo de moneda.</t>
+          <t>- Guarda como .xlsx (también se admite .csv).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>- moneda: codigo de tres letras (EUR, GBP, USD...).</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>- justificante: S o N.</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Sobre la columna descripcion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- Guarda como .xlsx (tambien se admite .csv).</t>
+          <t>Es la más importante. El agente lee ahí los matices que no están en los números:</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>si una cena incluía alcohol, a quién se invitó, qué feria justifica el precio del hotel.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Sobre la columna descripcion</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Es la mas importante. El agente lee ahi los matices que no estan en los numeros:</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Los dos bloques de la hoja</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>si una cena incluia alcohol, si habia transporte publico disponible, que clase de</t>
+          <t>G-001 a G-014: casos de política general. Incluyen dos cenas de 78 EUR idénticas</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>billete era. Escribe con naturalidad, como se lo contarias a un companero.</t>
+          <t>salvo por la descripción, un fraccionamiento de 28 + 29 EUR para esquivar el umbral</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>del justificante, descripciones insuficientes y un conflicto entre dos cláusulas.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Los 12 gastos de ejemplo incluyen casos deliberadamente dificiles.</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Puedes borrarlos y poner los tuyos, o dejarlos y anadir los tuyos debajo.</t>
+          <t>E-001 a E-008 (filas sombreadas): verificación de eventos. Todos son hoteles por</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>encima del límite justificados por una feria. Unos caen dentro de las fechas reales</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>del evento y otros fuera por pocos días. El último invoca una feria que no existe:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>es la prueba de si el agente está consultando fuentes o improvisando.</t>
         </is>
       </c>
     </row>

--- a/datos/plantilla_gastos.xlsx
+++ b/datos/plantilla_gastos.xlsx
@@ -447,17 +447,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="66" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -516,26 +516,26 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Luis Pardo</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>alojamiento</t>
+          <t>dietas</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Hotel una noche durante el congreso</t>
+          <t>Cena de trabajo</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -561,26 +561,26 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Luis Pardo</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>alojamiento</t>
+          <t>dietas</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Hotel una noche</t>
+          <t>Cena de trabajo con Elena Soto directora de compras de Nortek para cerrar la renovación del contrato</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Luis Pardo</t>
+          <t>Marta Gil</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -621,11 +621,11 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -634,12 +634,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Cena de trabajo</t>
+          <t>Comida de trabajo en La Tasquita</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -651,12 +651,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Luis Pardo</t>
+          <t>Marta Gil</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -666,11 +666,11 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -679,12 +679,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Cena de trabajo con Elena Soto directora de compras de Nortek para cerrar la renovación del contrato</t>
+          <t>Comida de trabajo en La Tasquita</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -696,26 +696,26 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Marta Gil</t>
+          <t>Jorge Sanz</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>dietas</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -724,12 +724,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Comida de trabajo en La Tasquita</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -741,26 +741,26 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Marta Gil</t>
+          <t>Luis Pardo</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>dietas</t>
+          <t>otros</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Comida de trabajo en La Tasquita</t>
+          <t>Varios</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>240</v>
+        <v>64</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Billete de avión en clase business</t>
+          <t>Taxi del hotel a la oficina; hay metro a 400 metros</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -831,308 +831,308 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Marta Gil</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>dietas</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Comida con el equipo de compras de Alvasa para presentar la nueva gama</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>E-001</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Ana Ruiz</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>E-002</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Ana Ruiz</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>E-003</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Luis Pardo</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante South Summit en La Nave</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>E-004</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Marta Gil</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>E-005</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Marta Gil</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>E-006</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>Jorge Sanz</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>otros</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>G-009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Clara Vega</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>dietas</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Almuerzo de equipo</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>G-010</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Clara Vega</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>dietas</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Almuerzo de equipo</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>G-011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Ana Ruiz</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>alojamiento</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Bilbao</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Hotel una noche</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>G-012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Jorge Sanz</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>transporte</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Taxi del hotel a la oficina; hay metro a 400 metros</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>G-013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Luis Pardo</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>otros</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Varios</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>G-014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Marta Gil</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>dietas</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Comida con el equipo de compras de Alvasa para presentar la nueva gama</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="F15" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante el Foro BAIDATA, Semana de la Economía del Dato</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1141,17 +1141,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>E-001</t>
+          <t>E-007</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Jorge Sanz</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1161,11 +1161,11 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Bilbao</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+          <t>Hotel una noche durante el Foro BAIDATA, Semana de la Economía del Dato</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1186,17 +1186,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>E-002</t>
+          <t>E-008</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Clara Vega</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1206,11 +1206,11 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Bilbao</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -1219,280 +1219,10 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+          <t>Hotel una noche durante la Feria Internacional del Calzado de Bilbao</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>E-003</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Luis Pardo</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>alojamiento</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>230</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Hotel una noche durante South Summit en La Nave</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>E-004</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Luis Pardo</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>alojamiento</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>205</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Hotel una noche durante Sports Summit Madrid</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>E-005</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Marta Gil</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>alojamiento</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>180</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>E-006</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Marta Gil</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>alojamiento</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>180</v>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>E-007</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Jorge Sanz</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>alojamiento</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Hotel una noche durante el Foro BAIDATA, Semana de la Economía del Dato</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>E-008</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Jorge Sanz</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>alojamiento</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Hotel una noche durante la Feria Internacional del Calzado de Bilbao</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1517,10 +1247,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="104" customWidth="1" min="1" max="1"/>
+    <col width="106" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1553,121 +1283,145 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>- No cambies los nombres de la fila 1 ni el orden de las columnas.</t>
+          <t>- No cambies los nombres de la fila 1 ni el orden de las columnas.  - Máximo 40 filas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>- Máximo 40 filas de datos.</t>
+          <t>- fecha: AAAA-MM-DD   - categoria: alojamiento, dietas, transporte u otros</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>- fecha: formato AAAA-MM-DD.   - categoria: alojamiento, dietas, transporte u otros.</t>
+          <t>- importe: solo el número   - moneda: EUR, GBP...   - justificante: S o N</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>- importe: solo el número.   - moneda: EUR, GBP...   - justificante: S o N.</t>
+          <t>- Guarda como .xlsx (también se admite .csv).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>- Guarda como .xlsx (también se admite .csv).</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Sobre la columna descripcion</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Sobre la columna descripcion</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Es la más importante. El agente lee ahí lo que no está en los números: a quién se</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Es la más importante. El agente lee ahí los matices que no están en los números:</t>
+          <t>invitó, si había alternativa de transporte, qué feria justifica el precio del hotel.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>si una cena incluía alcohol, a quién se invitó, qué feria justifica el precio del hotel.</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Los dos bloques de la hoja</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Los dos bloques de la hoja</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G-001 a G-014: casos de política general. Incluyen dos cenas de 78 EUR idénticas</t>
+          <t>G-001 a G-008 · interpretación. Ninguno se resuelve comparando cifras:</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>salvo por la descripción, un fraccionamiento de 28 + 29 EUR para esquivar el umbral</t>
+          <t xml:space="preserve">  · G-001 y G-002: misma cena de 78 EUR; solo una identifica a la invitada.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>del justificante, descripciones insuficientes y un conflicto entre dos cláusulas.</t>
+          <t xml:space="preserve">  · G-003 y G-004: 28 + 29 EUR el mismo día en el mismo sitio, sin justificante.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · G-005 y G-006: descripciones insuficientes para identificar la finalidad.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E-001 a E-008 (filas sombreadas): verificación de eventos. Todos son hoteles por</t>
+          <t xml:space="preserve">  · G-007: taxi habiendo metro a 400 metros.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>encima del límite justificados por una feria. Unos caen dentro de las fechas reales</t>
+          <t xml:space="preserve">  · G-008: comida con cliente de 86 EUR; dos cláusulas en conflicto.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>del evento y otros fuera por pocos días. El último invoca una feria que no existe:</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>es la prueba de si el agente está consultando fuentes o improvisando.</t>
+          <t>E-001 a E-008 · verificación de eventos (filas sombreadas). Todos son hoteles por</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>encima del límite justificados por una feria, y todos quedarían cubiertos por la</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>excepción del 60% si el evento fuese válido. Lo único que decide es la verificación:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cuatro caen dentro de las fechas reales, tres las invocan en un mes en el que la</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>feria no se celebra, y E-008 invoca una feria que no existe.</t>
         </is>
       </c>
     </row>

--- a/datos/plantilla_gastos.xlsx
+++ b/datos/plantilla_gastos.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -701,12 +701,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>transporte</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Taxi del hotel a la oficina; hay metro a 400 metros</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -741,26 +741,26 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Luis Pardo</t>
+          <t>Marta Gil</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>otros</t>
+          <t>dietas</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -769,100 +769,100 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Varios</t>
+          <t>Comida con el equipo de compras de Alvasa para presentar la nueva gama</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>G-007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Jorge Sanz</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>transporte</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>E-001</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Ana Ruiz</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Taxi del hotel a la oficina; hay metro a 400 metros</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>G-008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Marta Gil</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>dietas</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>E-002</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Ana Ruiz</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>alojamiento</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Comida con el equipo de compras de Alvasa para presentar la nueva gama</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -871,17 +871,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>E-001</t>
+          <t>E-003</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Luis Pardo</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+          <t>Hotel una noche durante South Summit en La Nave</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -916,17 +916,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>E-002</t>
+          <t>E-004</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Marta Gil</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -936,11 +936,11 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Hotel una noche durante TECMA, Feria Internacional de Urbanismo y Medio Ambiente</t>
+          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -961,17 +961,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>E-003</t>
+          <t>E-005</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Luis Pardo</t>
+          <t>Marta Gil</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -981,11 +981,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Hotel una noche durante South Summit en La Nave</t>
+          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1006,17 +1006,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>E-004</t>
+          <t>E-006</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Marta Gil</t>
+          <t>Jorge Sanz</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1026,11 +1026,11 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Bilbao</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
+          <t>Hotel una noche durante el Foro BAIDATA, Semana de la Economía del Dato</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>E-005</t>
+          <t>E-007</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Marta Gil</t>
+          <t>Jorge Sanz</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1071,11 +1071,11 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Bilbao</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Hotel una noche durante ExpoNadó, feria profesional de puericultura</t>
+          <t>Hotel una noche durante el Foro BAIDATA, Semana de la Economía del Dato</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1096,17 +1096,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>E-006</t>
+          <t>E-008</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Jorge Sanz</t>
+          <t>Clara Vega</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1129,100 +1129,10 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Hotel una noche durante el Foro BAIDATA, Semana de la Economía del Dato</t>
+          <t>Hotel una noche durante la Feria Internacional del Calzado de Bilbao</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>E-007</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Jorge Sanz</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>alojamiento</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Hotel una noche durante el Foro BAIDATA, Semana de la Economía del Dato</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>E-008</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Clara Vega</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>alojamiento</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Hotel una noche durante la Feria Internacional del Calzado de Bilbao</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
